--- a/ch_07_forecasting_time_series/ch_07.xlsx
+++ b/ch_07_forecasting_time_series/ch_07.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_07_forecasting_time_series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA00AE74-22E5-42BA-B682-C3F7448B58EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AE34CC-4D84-4317-8E4D-1FED0537283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -1032,10 +1032,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1054,7 +1054,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}" name="passengers" displayName="passengers" ref="A1:B145" totalsRowShown="0">
   <autoFilter ref="A1:B145" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{D51D0BEF-BFC7-4F34-B98C-315FEBBB8A48}" name="passengers"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1065,7 +1065,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}" name="shampoo" displayName="shampoo" ref="A1:B37" totalsRowShown="0">
   <autoFilter ref="A1:B37" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{1B629950-5F4A-4F2E-B795-D39EC6984B40}" name="sales"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1390,13 +1390,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30AC0CE-AC4D-4F0F-87BF-920A22749676}">
   <dimension ref="A1:B145"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="12.0703125" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A110" s="1" t="s">
         <v>108</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A111" s="1" t="s">
         <v>109</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A112" s="1" t="s">
         <v>110</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A113" s="1" t="s">
         <v>111</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A114" s="1" t="s">
         <v>112</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A115" s="1" t="s">
         <v>113</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A116" s="1" t="s">
         <v>114</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A118" s="1" t="s">
         <v>116</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A119" s="1" t="s">
         <v>117</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A120" s="1" t="s">
         <v>118</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A122" s="1" t="s">
         <v>120</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A123" s="1" t="s">
         <v>121</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A124" s="1" t="s">
         <v>122</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A125" s="1" t="s">
         <v>123</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A126" s="1" t="s">
         <v>124</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A127" s="1" t="s">
         <v>125</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A128" s="1" t="s">
         <v>126</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A129" s="1" t="s">
         <v>127</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A130" s="1" t="s">
         <v>128</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A131" s="1" t="s">
         <v>129</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A132" s="1" t="s">
         <v>130</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A133" s="1" t="s">
         <v>131</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A134" s="1" t="s">
         <v>132</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A135" s="1" t="s">
         <v>133</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A136" s="1" t="s">
         <v>134</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A137" s="1" t="s">
         <v>135</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A138" s="1" t="s">
         <v>136</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A140" s="1" t="s">
         <v>138</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A141" s="1" t="s">
         <v>139</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A142" s="1" t="s">
         <v>140</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A143" s="1" t="s">
         <v>141</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A145" s="1" t="s">
         <v>143</v>
       </c>
@@ -2567,12 +2567,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF831C9-C517-44BA-811F-F102BEB016DE}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>144</v>
       </c>
@@ -2580,289 +2580,289 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" s="2">
-        <v>46023</v>
+        <v>36526</v>
       </c>
       <c r="B2">
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A3" s="2">
-        <v>46024</v>
+        <v>36557</v>
       </c>
       <c r="B3">
         <v>145.9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A4" s="2">
-        <v>46025</v>
+        <v>36586</v>
       </c>
       <c r="B4">
         <v>183.1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A5" s="2">
-        <v>46026</v>
+        <v>36617</v>
       </c>
       <c r="B5">
         <v>119.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A6" s="2">
-        <v>46027</v>
+        <v>36647</v>
       </c>
       <c r="B6">
         <v>180.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A7" s="2">
-        <v>46028</v>
+        <v>36678</v>
       </c>
       <c r="B7">
         <v>168.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A8" s="2">
-        <v>46029</v>
+        <v>36708</v>
       </c>
       <c r="B8">
         <v>231.8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="2">
-        <v>46030</v>
+        <v>36739</v>
       </c>
       <c r="B9">
         <v>224.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A10" s="2">
-        <v>46031</v>
+        <v>36770</v>
       </c>
       <c r="B10">
         <v>192.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A11" s="2">
-        <v>46032</v>
+        <v>36800</v>
       </c>
       <c r="B11">
         <v>122.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A12" s="2">
-        <v>46033</v>
+        <v>36831</v>
       </c>
       <c r="B12">
         <v>336.5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A13" s="2">
-        <v>46034</v>
+        <v>36861</v>
       </c>
       <c r="B13">
         <v>185.9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A14" s="2">
-        <v>46054</v>
+        <v>36892</v>
       </c>
       <c r="B14">
         <v>194.3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A15" s="2">
-        <v>46055</v>
+        <v>36923</v>
       </c>
       <c r="B15">
         <v>149.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A16" s="2">
-        <v>46056</v>
+        <v>36951</v>
       </c>
       <c r="B16">
         <v>210.1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A17" s="2">
-        <v>46057</v>
+        <v>36982</v>
       </c>
       <c r="B17">
         <v>273.3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A18" s="2">
-        <v>46058</v>
+        <v>37012</v>
       </c>
       <c r="B18">
         <v>191.4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A19" s="2">
-        <v>46059</v>
+        <v>37043</v>
       </c>
       <c r="B19">
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A20" s="2">
-        <v>46060</v>
+        <v>37073</v>
       </c>
       <c r="B20">
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A21" s="2">
-        <v>46061</v>
+        <v>37104</v>
       </c>
       <c r="B21">
         <v>303.60000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A22" s="2">
-        <v>46062</v>
+        <v>37135</v>
       </c>
       <c r="B22">
         <v>289.89999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A23" s="2">
-        <v>46063</v>
+        <v>37165</v>
       </c>
       <c r="B23">
         <v>421.6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A24" s="2">
-        <v>46064</v>
+        <v>37196</v>
       </c>
       <c r="B24">
         <v>264.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A25" s="2">
-        <v>46065</v>
+        <v>37226</v>
       </c>
       <c r="B25">
         <v>342.3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A26" s="2">
-        <v>46082</v>
+        <v>37257</v>
       </c>
       <c r="B26">
         <v>339.7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A27" s="2">
-        <v>46083</v>
+        <v>37288</v>
       </c>
       <c r="B27">
         <v>440.4</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A28" s="2">
-        <v>46084</v>
+        <v>37316</v>
       </c>
       <c r="B28">
         <v>315.89999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A29" s="2">
-        <v>46085</v>
+        <v>37347</v>
       </c>
       <c r="B29">
         <v>439.3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A30" s="2">
-        <v>46086</v>
+        <v>37377</v>
       </c>
       <c r="B30">
         <v>401.3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A31" s="2">
-        <v>46087</v>
+        <v>37408</v>
       </c>
       <c r="B31">
         <v>437.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A32" s="2">
-        <v>46088</v>
+        <v>37438</v>
       </c>
       <c r="B32">
         <v>575.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A33" s="2">
-        <v>46089</v>
+        <v>37469</v>
       </c>
       <c r="B33">
         <v>407.6</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A34" s="2">
-        <v>46090</v>
+        <v>37500</v>
       </c>
       <c r="B34">
         <v>682</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A35" s="2">
-        <v>46091</v>
+        <v>37530</v>
       </c>
       <c r="B35">
         <v>475.3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A36" s="2">
-        <v>46092</v>
+        <v>37561</v>
       </c>
       <c r="B36">
         <v>581.29999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A37" s="2">
-        <v>46093</v>
+        <v>37591</v>
       </c>
       <c r="B37">
         <v>646.9</v>
